--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z839"/>
+  <dimension ref="A1:Z841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49282,14 +49282,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5140-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5140-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49629,14 +49629,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49648,8 +49648,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G836" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49686,14 +49691,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49705,13 +49710,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G837" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49748,14 +49748,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -49807,7 +49807,7 @@
       </c>
       <c r="R838" s="2" t="inlineStr"/>
     </row>
-    <row r="839">
+    <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
           <t>A 6007-2024</t>
@@ -49817,7 +49817,7 @@
         <v>45336</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45337</v>
+        <v>45338</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49863,6 +49863,120 @@
         <v>0</v>
       </c>
       <c r="R839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840" ht="15" customHeight="1">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>A 6175-2024</t>
+        </is>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C840" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0</v>
+      </c>
+      <c r="R840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>A 6183-2024</t>
+        </is>
+      </c>
+      <c r="B841" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C841" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G841" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L841" t="n">
+        <v>0</v>
+      </c>
+      <c r="M841" t="n">
+        <v>0</v>
+      </c>
+      <c r="N841" t="n">
+        <v>0</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0</v>
+      </c>
+      <c r="P841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q841" t="n">
+        <v>0</v>
+      </c>
+      <c r="R841" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z841"/>
+  <dimension ref="A1:Z842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49574,7 +49574,7 @@
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49629,14 +49629,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49648,13 +49648,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G836" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49691,14 +49686,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49710,8 +49705,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G837" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49748,14 +49748,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49767,13 +49767,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G838" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -49810,14 +49805,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 6007-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
-        <v>45336</v>
+        <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49829,8 +49824,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G839" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49867,71 +49867,71 @@
     <row r="840" ht="15" customHeight="1">
       <c r="A840" t="inlineStr">
         <is>
+          <t>A 6007-2024</t>
+        </is>
+      </c>
+      <c r="B840" s="1" t="n">
+        <v>45336</v>
+      </c>
+      <c r="C840" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G840" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H840" t="n">
+        <v>0</v>
+      </c>
+      <c r="I840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L840" t="n">
+        <v>0</v>
+      </c>
+      <c r="M840" t="n">
+        <v>0</v>
+      </c>
+      <c r="N840" t="n">
+        <v>0</v>
+      </c>
+      <c r="O840" t="n">
+        <v>0</v>
+      </c>
+      <c r="P840" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q840" t="n">
+        <v>0</v>
+      </c>
+      <c r="R840" s="2" t="inlineStr"/>
+    </row>
+    <row r="841" ht="15" customHeight="1">
+      <c r="A841" t="inlineStr">
+        <is>
           <t>A 6175-2024</t>
-        </is>
-      </c>
-      <c r="B840" s="1" t="n">
-        <v>45337</v>
-      </c>
-      <c r="C840" s="1" t="n">
-        <v>45338</v>
-      </c>
-      <c r="D840" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="E840" t="inlineStr">
-        <is>
-          <t>MORA</t>
-        </is>
-      </c>
-      <c r="G840" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="H840" t="n">
-        <v>0</v>
-      </c>
-      <c r="I840" t="n">
-        <v>0</v>
-      </c>
-      <c r="J840" t="n">
-        <v>0</v>
-      </c>
-      <c r="K840" t="n">
-        <v>0</v>
-      </c>
-      <c r="L840" t="n">
-        <v>0</v>
-      </c>
-      <c r="M840" t="n">
-        <v>0</v>
-      </c>
-      <c r="N840" t="n">
-        <v>0</v>
-      </c>
-      <c r="O840" t="n">
-        <v>0</v>
-      </c>
-      <c r="P840" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q840" t="n">
-        <v>0</v>
-      </c>
-      <c r="R840" s="2" t="inlineStr"/>
-    </row>
-    <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>A 6183-2024</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49944,39 +49944,96 @@
         </is>
       </c>
       <c r="G841" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H841" t="n">
+        <v>0</v>
+      </c>
+      <c r="I841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L841" t="n">
+        <v>0</v>
+      </c>
+      <c r="M841" t="n">
+        <v>0</v>
+      </c>
+      <c r="N841" t="n">
+        <v>0</v>
+      </c>
+      <c r="O841" t="n">
+        <v>0</v>
+      </c>
+      <c r="P841" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q841" t="n">
+        <v>0</v>
+      </c>
+      <c r="R841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>A 6183-2024</t>
+        </is>
+      </c>
+      <c r="B842" s="1" t="n">
+        <v>45337</v>
+      </c>
+      <c r="C842" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G842" t="n">
         <v>7.9</v>
       </c>
-      <c r="H841" t="n">
-        <v>0</v>
-      </c>
-      <c r="I841" t="n">
-        <v>0</v>
-      </c>
-      <c r="J841" t="n">
-        <v>0</v>
-      </c>
-      <c r="K841" t="n">
-        <v>0</v>
-      </c>
-      <c r="L841" t="n">
-        <v>0</v>
-      </c>
-      <c r="M841" t="n">
-        <v>0</v>
-      </c>
-      <c r="N841" t="n">
-        <v>0</v>
-      </c>
-      <c r="O841" t="n">
-        <v>0</v>
-      </c>
-      <c r="P841" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q841" t="n">
-        <v>0</v>
-      </c>
-      <c r="R841" s="2" t="inlineStr"/>
+      <c r="H842" t="n">
+        <v>0</v>
+      </c>
+      <c r="I842" t="n">
+        <v>0</v>
+      </c>
+      <c r="J842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L842" t="n">
+        <v>0</v>
+      </c>
+      <c r="M842" t="n">
+        <v>0</v>
+      </c>
+      <c r="N842" t="n">
+        <v>0</v>
+      </c>
+      <c r="O842" t="n">
+        <v>0</v>
+      </c>
+      <c r="P842" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q842" t="n">
+        <v>0</v>
+      </c>
+      <c r="R842" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49282,14 +49282,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 5140-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5140-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,8 +49529,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49572,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49586,13 +49591,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G835" t="n">
-        <v>0.1</v>
+        <v>8.4</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49629,14 +49629,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49686,14 +49686,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49707,7 +49707,7 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G837" t="n">
@@ -49748,14 +49748,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49767,8 +49767,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G838" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -49805,14 +49810,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49824,13 +49829,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G839" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49924,14 +49924,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 6175-2024</t>
+          <t>A 6183-2024</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -49981,14 +49981,14 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 6183-2024</t>
+          <t>A 6175-2024</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45340</v>
+        <v>45343</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>7.9</v>
+        <v>16.1</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48940,14 +48940,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 3107-2024</t>
+          <t>A 3219-2024</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -48997,14 +48997,14 @@
     <row r="825" ht="15" customHeight="1">
       <c r="A825" t="inlineStr">
         <is>
-          <t>A 3219-2024</t>
+          <t>A 3107-2024</t>
         </is>
       </c>
       <c r="B825" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,13 +49529,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G834" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49579,7 +49574,7 @@
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49636,7 +49631,7 @@
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49686,14 +49681,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49707,7 +49702,7 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G837" t="n">
@@ -49748,14 +49743,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49769,11 +49764,11 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G838" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -49810,14 +49805,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49829,8 +49824,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z842"/>
+  <dimension ref="A1:Z843"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48940,14 +48940,14 @@
     <row r="824" ht="15" customHeight="1">
       <c r="A824" t="inlineStr">
         <is>
-          <t>A 3219-2024</t>
+          <t>A 3107-2024</t>
         </is>
       </c>
       <c r="B824" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48960,7 +48960,7 @@
         </is>
       </c>
       <c r="G824" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -48997,14 +48997,14 @@
     <row r="825" ht="15" customHeight="1">
       <c r="A825" t="inlineStr">
         <is>
-          <t>A 3107-2024</t>
+          <t>A 3219-2024</t>
         </is>
       </c>
       <c r="B825" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         </is>
       </c>
       <c r="G825" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="H825" t="n">
         <v>0</v>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,8 +49529,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49572,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49586,8 +49591,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G835" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49624,14 +49634,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49644,7 +49654,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49681,14 +49691,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49700,13 +49710,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G837" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49750,7 +49755,7 @@
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49805,14 +49810,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49824,13 +49829,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G839" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49924,14 +49924,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 6183-2024</t>
+          <t>A 6175-2024</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>7.9</v>
+        <v>16.1</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -49978,17 +49978,17 @@
       </c>
       <c r="R841" s="2" t="inlineStr"/>
     </row>
-    <row r="842">
+    <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 6175-2024</t>
+          <t>A 6183-2024</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -50034,6 +50034,63 @@
         <v>0</v>
       </c>
       <c r="R842" s="2" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>A 7116-2024</t>
+        </is>
+      </c>
+      <c r="B843" s="1" t="n">
+        <v>45343</v>
+      </c>
+      <c r="C843" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G843" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H843" t="n">
+        <v>0</v>
+      </c>
+      <c r="I843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K843" t="n">
+        <v>0</v>
+      </c>
+      <c r="L843" t="n">
+        <v>0</v>
+      </c>
+      <c r="M843" t="n">
+        <v>0</v>
+      </c>
+      <c r="N843" t="n">
+        <v>0</v>
+      </c>
+      <c r="O843" t="n">
+        <v>0</v>
+      </c>
+      <c r="P843" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q843" t="n">
+        <v>0</v>
+      </c>
+      <c r="R843" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z843"/>
+  <dimension ref="A1:Z844"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49282,14 +49282,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5140-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5140-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,13 +49529,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G834" t="n">
-        <v>0.1</v>
+        <v>8.4</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49572,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49591,13 +49586,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F835" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G835" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49634,14 +49624,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49654,7 +49644,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49691,14 +49681,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49710,8 +49700,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G837" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49748,14 +49743,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49769,7 +49764,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -49810,14 +49805,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49829,8 +49824,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="R842" s="2" t="inlineStr"/>
     </row>
-    <row r="843">
+    <row r="843" ht="15" customHeight="1">
       <c r="A843" t="inlineStr">
         <is>
           <t>A 7116-2024</t>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45345</v>
+        <v>45346</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50091,6 +50091,63 @@
         <v>0</v>
       </c>
       <c r="R843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>A 7414-2024</t>
+        </is>
+      </c>
+      <c r="B844" s="1" t="n">
+        <v>45345</v>
+      </c>
+      <c r="C844" s="1" t="n">
+        <v>45346</v>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G844" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H844" t="n">
+        <v>0</v>
+      </c>
+      <c r="I844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J844" t="n">
+        <v>0</v>
+      </c>
+      <c r="K844" t="n">
+        <v>0</v>
+      </c>
+      <c r="L844" t="n">
+        <v>0</v>
+      </c>
+      <c r="M844" t="n">
+        <v>0</v>
+      </c>
+      <c r="N844" t="n">
+        <v>0</v>
+      </c>
+      <c r="O844" t="n">
+        <v>0</v>
+      </c>
+      <c r="P844" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q844" t="n">
+        <v>0</v>
+      </c>
+      <c r="R844" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49624,14 +49624,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49688,7 +49688,7 @@
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49812,7 +49812,7 @@
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49924,14 +49924,14 @@
     <row r="841" ht="15" customHeight="1">
       <c r="A841" t="inlineStr">
         <is>
-          <t>A 6175-2024</t>
+          <t>A 6183-2024</t>
         </is>
       </c>
       <c r="B841" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         </is>
       </c>
       <c r="G841" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H841" t="n">
         <v>0</v>
@@ -49981,14 +49981,14 @@
     <row r="842" ht="15" customHeight="1">
       <c r="A842" t="inlineStr">
         <is>
-          <t>A 6183-2024</t>
+          <t>A 6175-2024</t>
         </is>
       </c>
       <c r="B842" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         </is>
       </c>
       <c r="G842" t="n">
-        <v>7.9</v>
+        <v>16.1</v>
       </c>
       <c r="H842" t="n">
         <v>0</v>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45345</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>8.4</v>
+        <v>1.1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49624,14 +49624,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49643,8 +49643,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G836" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49688,7 +49693,7 @@
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49743,14 +49748,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49764,7 +49769,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -49805,14 +49810,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49824,13 +49829,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F839" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G839" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45345</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,8 +49529,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G834" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49572,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49587,7 +49592,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49624,14 +49629,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49649,7 +49654,7 @@
         </is>
       </c>
       <c r="G836" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49686,14 +49691,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49707,11 +49712,11 @@
       </c>
       <c r="F837" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G837" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49748,14 +49753,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49767,13 +49772,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F838" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G838" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -49810,14 +49810,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49830,7 +49830,7 @@
         </is>
       </c>
       <c r="G839" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45345</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49346,7 +49346,7 @@
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49403,7 +49403,7 @@
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49529,13 +49529,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F834" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G834" t="n">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49572,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49592,7 +49587,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49636,7 +49631,7 @@
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49691,14 +49686,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49710,13 +49705,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F837" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="G837" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49753,14 +49743,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49772,8 +49762,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G838" t="n">
-        <v>8.4</v>
+        <v>0.6</v>
       </c>
       <c r="H838" t="n">
         <v>0</v>
@@ -49810,14 +49805,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49829,8 +49824,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="G839" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50102,7 +50102,7 @@
         <v>45345</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z844"/>
+  <dimension ref="A1:Z846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48662,7 +48662,7 @@
         <v>45299</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45299</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45309</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>45310</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48890,7 +48890,7 @@
         <v>45310</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48947,7 +48947,7 @@
         <v>45316</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>45316</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45317</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45320</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45327</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45328</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49282,14 +49282,14 @@
     <row r="830" ht="15" customHeight="1">
       <c r="A830" t="inlineStr">
         <is>
-          <t>A 5140-2024</t>
+          <t>A 5217-2024</t>
         </is>
       </c>
       <c r="B830" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49302,7 +49302,7 @@
         </is>
       </c>
       <c r="G830" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="H830" t="n">
         <v>0</v>
@@ -49339,14 +49339,14 @@
     <row r="831" ht="15" customHeight="1">
       <c r="A831" t="inlineStr">
         <is>
-          <t>A 5217-2024</t>
+          <t>A 5134-2024</t>
         </is>
       </c>
       <c r="B831" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         </is>
       </c>
       <c r="G831" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="H831" t="n">
         <v>0</v>
@@ -49396,14 +49396,14 @@
     <row r="832" ht="15" customHeight="1">
       <c r="A832" t="inlineStr">
         <is>
-          <t>A 5134-2024</t>
+          <t>A 5140-2024</t>
         </is>
       </c>
       <c r="B832" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49416,7 +49416,7 @@
         </is>
       </c>
       <c r="G832" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H832" t="n">
         <v>0</v>
@@ -49460,7 +49460,7 @@
         <v>45332</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49510,14 +49510,14 @@
     <row r="834" ht="15" customHeight="1">
       <c r="A834" t="inlineStr">
         <is>
-          <t>A 5532-2024</t>
+          <t>A 5527-2024</t>
         </is>
       </c>
       <c r="B834" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         </is>
       </c>
       <c r="G834" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -49567,14 +49567,14 @@
     <row r="835" ht="15" customHeight="1">
       <c r="A835" t="inlineStr">
         <is>
-          <t>A 5540-2024</t>
+          <t>A 5532-2024</t>
         </is>
       </c>
       <c r="B835" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49587,7 +49587,7 @@
         </is>
       </c>
       <c r="G835" t="n">
-        <v>1.1</v>
+        <v>8.4</v>
       </c>
       <c r="H835" t="n">
         <v>0</v>
@@ -49624,14 +49624,14 @@
     <row r="836" ht="15" customHeight="1">
       <c r="A836" t="inlineStr">
         <is>
-          <t>A 5542-2024</t>
+          <t>A 5540-2024</t>
         </is>
       </c>
       <c r="B836" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49643,13 +49643,8 @@
           <t>MORA</t>
         </is>
       </c>
-      <c r="F836" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="G836" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
       <c r="H836" t="n">
         <v>0</v>
@@ -49686,14 +49681,14 @@
     <row r="837" ht="15" customHeight="1">
       <c r="A837" t="inlineStr">
         <is>
-          <t>A 5527-2024</t>
+          <t>A 5541-2024</t>
         </is>
       </c>
       <c r="B837" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49705,8 +49700,13 @@
           <t>MORA</t>
         </is>
       </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="G837" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H837" t="n">
         <v>0</v>
@@ -49743,14 +49743,14 @@
     <row r="838" ht="15" customHeight="1">
       <c r="A838" t="inlineStr">
         <is>
-          <t>A 5541-2024</t>
+          <t>A 5644-2024</t>
         </is>
       </c>
       <c r="B838" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
       </c>
       <c r="F838" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="G838" t="n">
@@ -49805,14 +49805,14 @@
     <row r="839" ht="15" customHeight="1">
       <c r="A839" t="inlineStr">
         <is>
-          <t>A 5644-2024</t>
+          <t>A 5542-2024</t>
         </is>
       </c>
       <c r="B839" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49826,11 +49826,11 @@
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="G839" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H839" t="n">
         <v>0</v>
@@ -49874,7 +49874,7 @@
         <v>45336</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>45337</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45337</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>45343</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
       </c>
       <c r="R843" s="2" t="inlineStr"/>
     </row>
-    <row r="844">
+    <row r="844" ht="15" customHeight="1">
       <c r="A844" t="inlineStr">
         <is>
           <t>A 7414-2024</t>
@@ -50102,7 +50102,7 @@
         <v>45345</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50148,6 +50148,120 @@
         <v>0</v>
       </c>
       <c r="R844" s="2" t="inlineStr"/>
+    </row>
+    <row r="845" ht="15" customHeight="1">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>A 7945-2024</t>
+        </is>
+      </c>
+      <c r="B845" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C845" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G845" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H845" t="n">
+        <v>0</v>
+      </c>
+      <c r="I845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K845" t="n">
+        <v>0</v>
+      </c>
+      <c r="L845" t="n">
+        <v>0</v>
+      </c>
+      <c r="M845" t="n">
+        <v>0</v>
+      </c>
+      <c r="N845" t="n">
+        <v>0</v>
+      </c>
+      <c r="O845" t="n">
+        <v>0</v>
+      </c>
+      <c r="P845" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q845" t="n">
+        <v>0</v>
+      </c>
+      <c r="R845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>A 7972-2024</t>
+        </is>
+      </c>
+      <c r="B846" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="C846" s="1" t="n">
+        <v>45351</v>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>MORA</t>
+        </is>
+      </c>
+      <c r="G846" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H846" t="n">
+        <v>0</v>
+      </c>
+      <c r="I846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J846" t="n">
+        <v>0</v>
+      </c>
+      <c r="K846" t="n">
+        <v>0</v>
+      </c>
+      <c r="L846" t="n">
+        <v>0</v>
+      </c>
+      <c r="M846" t="n">
+        <v>0</v>
+      </c>
+      <c r="N846" t="n">
+        <v>0</v>
+      </c>
+      <c r="O846" t="n">
+        <v>0</v>
+      </c>
+      <c r="P846" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q846" t="n">
+        <v>0</v>
+      </c>
+      <c r="R846" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt MORA.xlsx
+++ b/Översikt MORA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z846"/>
+  <dimension ref="A1:Z848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45118</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>44111</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>45079</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>45061</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>44125</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>43979</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>44957</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>43649</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>43801</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44150</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>44160</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>45092</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>45110</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>43371</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>44028</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>44364</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44915</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>44959</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>45077</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>45113</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45138</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>45232</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>45334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>43339</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>43346</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>43346</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>43346</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>43346</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>43346</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>43354</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>43360</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
         <v>43368</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>43371</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>43371</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>43374</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>43374</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>43377</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>43388</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         <v>43391</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>43396</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>43397</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>43402</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>43418</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>43423</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>43423</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>43430</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>43433</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>43434</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>43437</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>43437</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>43437</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>43437</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>43437</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>43438</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>43440</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>43440</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>43447</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>43455</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>43455</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>43455</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4895,7 +4895,7 @@
         <v>43455</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>43462</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>43467</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>43467</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>43469</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>43472</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>43474</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>43474</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>43476</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>43481</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>43482</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>43482</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>43483</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>43483</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>43483</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>43483</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>43483</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>43483</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>43483</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>43493</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>43493</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>43495</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>43495</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>43530</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>43545</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6355,7 +6355,7 @@
         <v>43546</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>43570</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>43572</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>43591</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>43594</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>43594</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>43601</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>43601</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>43602</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         <v>43612</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>43612</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>43623</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>43629</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         <v>43629</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>43629</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>43635</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>43635</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>43635</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>43636</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>43636</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>43640</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>43642</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>43643</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>43649</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>43649</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>43649</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>43649</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>43650</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>43651</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>43656</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>43661</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         <v>43664</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>43675</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>43675</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>43676</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>43682</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>43685</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>43692</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8561,7 +8561,7 @@
         <v>43692</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>43693</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>43698</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         <v>43703</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>43707</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43707</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>43707</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>43707</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>43718</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>43718</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>43718</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>43724</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>43724</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>43727</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         <v>43727</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>43731</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>43731</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>43733</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>43747</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>43748</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>43754</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>43761</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>43767</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>43768</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>43769</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>43769</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>43770</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>43782</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10187,7 +10187,7 @@
         <v>43782</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>43783</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>43784</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         <v>43787</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>43791</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>43791</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>43795</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>43802</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>43803</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>43804</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>43808</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>43810</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>43810</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>43810</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>43811</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>43815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>43817</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>43817</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>43826</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>43837</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>43844</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>43845</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>43857</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>43859</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>43865</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>43868</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>43871</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>43888</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>43896</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>43899</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>43906</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>43910</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>43917</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>43917</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>43935</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>43935</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>43938</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>43951</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>43958</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>43978</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>43984</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43987</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43987</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44005</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44006</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44006</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44022</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44032</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44032</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44032</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44047</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44055</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44057</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44062</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44064</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44067</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44074</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44074</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44076</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44081</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44100</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44109</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44109</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44118</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44130</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44133</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44137</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44138</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44138</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44139</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44141</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44141</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>44152</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>44155</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>44160</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>44160</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44160</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44169</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44180</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44180</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44186</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44187</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44194</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44194</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>44203</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44203</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44203</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44203</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44203</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44203</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15447,7 +15447,7 @@
         <v>44203</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44203</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44204</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44210</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44243</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>44244</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>44244</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15846,7 +15846,7 @@
         <v>44266</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>44295</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44301</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44301</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44309</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         <v>44313</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>44314</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16250,7 +16250,7 @@
         <v>44326</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16307,7 +16307,7 @@
         <v>44337</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44343</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44347</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>44362</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>44363</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>44365</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>44365</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44365</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44368</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44368</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44369</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44369</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44379</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44382</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44382</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44383</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44383</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44389</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44389</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44389</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44410</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44413</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44413</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44417</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44421</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44421</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44421</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44423</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44427</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44427</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44432</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>44435</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>44435</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44438</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44438</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44440</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44441</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44441</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44447</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44449</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44451</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>44455</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>44455</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         <v>44455</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>44458</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>44459</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44462</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44466</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>44473</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>44473</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44480</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44482</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>44484</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44487</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44488</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>44488</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>44489</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44490</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44494</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19928,7 +19928,7 @@
         <v>44497</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44505</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44505</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44505</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
         <v>44508</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44509</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44515</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>44515</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>44515</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>44515</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>44516</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>44516</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44517</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>44517</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>44518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20813,7 +20813,7 @@
         <v>44519</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>44522</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>44523</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20984,7 +20984,7 @@
         <v>44523</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>44523</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44525</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44529</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21222,7 +21222,7 @@
         <v>44530</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>44531</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>44533</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>44533</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>44543</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44545</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
         <v>44545</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21636,7 +21636,7 @@
         <v>44545</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44546</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21755,7 +21755,7 @@
         <v>44546</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44547</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44553</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>44564</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44578</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44578</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44581</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>44581</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>44589</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>44589</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>44600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44601</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>44601</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>44608</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>44609</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>44609</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44613</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>44615</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>44617</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>44620</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22900,7 +22900,7 @@
         <v>44630</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>44630</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>44636</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>44642</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>44644</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44645</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44656</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44656</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44658</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44658</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>44659</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>44662</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>44673</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23646,7 +23646,7 @@
         <v>44673</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44678</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>44680</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>44692</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44694</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>44699</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44705</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>44720</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44721</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>44722</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44722</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44725</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>44725</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>44725</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24459,7 +24459,7 @@
         <v>44725</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44726</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>44726</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44732</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>44742</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>44742</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>44747</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44749</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44755</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44768</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25049,7 +25049,7 @@
         <v>44773</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44775</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>44781</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44781</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25277,7 +25277,7 @@
         <v>44782</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>44783</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44788</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>44788</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>44788</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>44788</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>44789</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>44789</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25738,7 +25738,7 @@
         <v>44796</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25795,7 +25795,7 @@
         <v>44796</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44796</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44796</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44796</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44804</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44809</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44810</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>44810</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>44811</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>44812</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>44813</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44817</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26504,7 +26504,7 @@
         <v>44819</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>44819</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>44830</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>44830</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>44831</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44832</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44832</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44837</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44837</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44838</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44838</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>44838</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>44844</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>44845</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>44845</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44845</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>44847</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>44848</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>44851</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>44852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>44853</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44858</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44858</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>44858</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>44859</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>44859</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>44861</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44865</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44867</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44869</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44874</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44874</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44875</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44876</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>44882</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44883</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>44886</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44886</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>44886</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>44886</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44887</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>44887</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>44888</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>44889</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29047,7 +29047,7 @@
         <v>44889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29109,7 +29109,7 @@
         <v>44890</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29166,7 +29166,7 @@
         <v>44893</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>44893</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44894</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44894</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>44896</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44897</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>44897</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>44898</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>44900</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29679,7 +29679,7 @@
         <v>44900</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>44901</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>44902</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29850,7 +29850,7 @@
         <v>44903</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>44906</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29964,7 +29964,7 @@
         <v>44907</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>44907</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>44909</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>44911</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>44915</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30249,7 +30249,7 @@
         <v>44915</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44915</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>44915</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>44915</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44916</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>44917</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44922</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>44930</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>44937</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30762,7 +30762,7 @@
         <v>44937</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>44937</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         <v>44937</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30933,7 +30933,7 @@
         <v>44942</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44942</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>44942</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>44945</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>44946</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>44949</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>44953</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31332,7 +31332,7 @@
         <v>44953</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>44953</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44953</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31503,7 +31503,7 @@
         <v>44953</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>44956</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31617,7 +31617,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31674,7 +31674,7 @@
         <v>44956</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>44957</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>44957</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>44957</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>44958</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44958</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>44958</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44959</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32140,7 +32140,7 @@
         <v>44964</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>44967</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         <v>44971</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32311,7 +32311,7 @@
         <v>44978</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32368,7 +32368,7 @@
         <v>44979</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44984</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44986</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>44995</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45000</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45001</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45001</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45002</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>45007</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45008</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45013</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>45015</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45019</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45019</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45021</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45029</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45033</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>45036</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33419,7 +33419,7 @@
         <v>45042</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45043</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45044</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>45044</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>45049</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33704,7 +33704,7 @@
         <v>45056</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>45056</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33818,7 +33818,7 @@
         <v>45056</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33875,7 +33875,7 @@
         <v>45057</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45057</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33999,7 +33999,7 @@
         <v>45061</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45061</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45061</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>45063</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>45068</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45068</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45068</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45070</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34475,7 +34475,7 @@
         <v>45071</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34532,7 +34532,7 @@
         <v>45072</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45072</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34646,7 +34646,7 @@
         <v>45072</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45072</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45072</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45072</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45075</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45075</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>45075</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35045,7 +35045,7 @@
         <v>45077</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35102,7 +35102,7 @@
         <v>45077</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>45078</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45079</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45079</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45084</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45084</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45084</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45084</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45086</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45089</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45090</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45090</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35791,7 +35791,7 @@
         <v>45090</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45090</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45090</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45090</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45090</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45090</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45093</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45096</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45098</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45098</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>45099</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36423,7 +36423,7 @@
         <v>45099</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36480,7 +36480,7 @@
         <v>45099</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45103</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36594,7 +36594,7 @@
         <v>45104</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45104</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>45104</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36770,7 +36770,7 @@
         <v>45105</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36827,7 +36827,7 @@
         <v>45105</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45105</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36941,7 +36941,7 @@
         <v>45105</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45105</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45105</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45113</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45114</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45114</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45132</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45138</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45138</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45145</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45145</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37578,7 +37578,7 @@
         <v>45145</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>45145</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>45147</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45147</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>45153</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>45153</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45159</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45159</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>45159</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45159</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45160</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38262,7 +38262,7 @@
         <v>45161</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>45162</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45162</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38433,7 +38433,7 @@
         <v>45162</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45162</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45166</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38604,7 +38604,7 @@
         <v>45166</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38661,7 +38661,7 @@
         <v>45167</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45167</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45168</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45168</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38889,7 +38889,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38946,7 +38946,7 @@
         <v>45170</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>45173</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39070,7 +39070,7 @@
         <v>45174</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>45174</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39184,7 +39184,7 @@
         <v>45175</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>45175</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39298,7 +39298,7 @@
         <v>45177</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45180</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39422,7 +39422,7 @@
         <v>45180</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45184</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39541,7 +39541,7 @@
         <v>45184</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39603,7 +39603,7 @@
         <v>45184</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39665,7 +39665,7 @@
         <v>45187</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39727,7 +39727,7 @@
         <v>45188</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>45188</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39841,7 +39841,7 @@
         <v>45188</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39898,7 +39898,7 @@
         <v>45188</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>45188</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45188</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45190</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45190</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45190</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>45191</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45194</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45194</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40411,7 +40411,7 @@
         <v>45196</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45196</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>45196</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45197</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40644,7 +40644,7 @@
         <v>45198</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40701,7 +40701,7 @@
         <v>45198</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45198</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45202</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40877,7 +40877,7 @@
         <v>45202</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45202</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45203</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45203</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41120,7 +41120,7 @@
         <v>45203</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>45203</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45204</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>45204</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45205</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>45205</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45205</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41529,7 +41529,7 @@
         <v>45205</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41586,7 +41586,7 @@
         <v>45209</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>45210</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>45210</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41757,7 +41757,7 @@
         <v>45210</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>45212</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41871,7 +41871,7 @@
         <v>45215</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>45215</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45215</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45217</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45217</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45219</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42275,7 +42275,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45219</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>45222</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42508,7 +42508,7 @@
         <v>45222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45222</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>45222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45223</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45225</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42798,7 +42798,7 @@
         <v>45226</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42855,7 +42855,7 @@
         <v>45226</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>45226</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
         <v>45226</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45226</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>45228</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43145,7 +43145,7 @@
         <v>45228</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43202,7 +43202,7 @@
         <v>45228</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43259,7 +43259,7 @@
         <v>45228</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43316,7 +43316,7 @@
         <v>45229</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>45229</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>45229</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45229</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45231</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43601,7 +43601,7 @@
         <v>45231</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43658,7 +43658,7 @@
         <v>45231</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43720,7 +43720,7 @@
         <v>45232</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43777,7 +43777,7 @@
         <v>45232</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>45232</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45232</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45232</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45232</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45232</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45232</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45236</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45236</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45237</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>45238</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45239</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45239</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>45240</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45240</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>45240</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45240</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45240</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45240</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45240</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45240</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45240</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45244</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45244</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45244</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45245</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45245</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45246</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45247</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45247</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45247</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45247</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45252</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45252</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45252</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45253</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45253</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45253</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45253</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45253</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45254</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45254</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45257</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>45257</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45258</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>45259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45259</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45259</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46523,7 +46523,7 @@
         <v>45259</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45260</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>45260</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>45260</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46751,7 +46751,7 @@
         <v>45260</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46808,7 +46808,7 @@
         <v>45260</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>45264</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45264</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46989,7 +46989,7 @@
         <v>45264</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47051,7 +47051,7 @@
         <v>45264</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>45264</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47165,7 +47165,7 @@
         <v>45264</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45264</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47284,7 +47284,7 @@
         <v>45264</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47346,7 +47346,7 @@
         <v>45264</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47408,7 +47408,7 @@
         <v>45264</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>45264</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47522,7 +47522,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>45265</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45265</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45265</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47750,7 +47750,7 @@
         <v>45266</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47807,7 +47807,7 @@
         <v>45266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47864,7 +47864,7 @@
         <v>45271</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47921,7 +47921,7 @@
         <v>45272</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47978,7 +47978,7 @@
         <v>45272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48035,7 +48035,7 @@
         <v>45273</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>45278</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48149,7 +48149,7 @@
         <v>45279</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45279</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48263,7 +48263,7 @@
         <v>45279</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48320,7 +48320,7 @@
         <v>45280</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48377,7 +48377,7 @@
         <v>45280</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48434,7 +48434,7 @@
         <v>45296</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48491,7 +48491,7 @@
         <v>45296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45296</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48605,7 +48605,7 @@
         <v>45299</v>
       </c>
 